--- a/AC_2009/AC_032.xlsx
+++ b/AC_2009/AC_032.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V295"/>
+  <dimension ref="A1:V297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -516,6 +597,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -21162,85 +21244,246 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C295" s="7">
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="inlineStr"/>
+      <c r="C295" s="10">
         <f>SUM(C6:C294)</f>
         <v/>
       </c>
-      <c r="D295" s="7">
+      <c r="D295" s="10">
         <f>SUM(D6:D294)</f>
         <v/>
       </c>
-      <c r="E295" s="7">
+      <c r="E295" s="10">
         <f>SUM(E6:E294)</f>
         <v/>
       </c>
-      <c r="F295" s="7">
+      <c r="F295" s="10">
         <f>SUM(F6:F294)</f>
         <v/>
       </c>
-      <c r="G295" s="7">
+      <c r="G295" s="10">
         <f>SUM(G6:G294)</f>
         <v/>
       </c>
-      <c r="H295" s="7">
+      <c r="H295" s="10">
         <f>SUM(H6:H294)</f>
         <v/>
       </c>
-      <c r="I295" s="7">
+      <c r="I295" s="10">
         <f>SUM(I6:I294)</f>
         <v/>
       </c>
-      <c r="J295" s="7">
+      <c r="J295" s="10">
         <f>SUM(J6:J294)</f>
         <v/>
       </c>
-      <c r="K295" s="7">
+      <c r="K295" s="10">
         <f>SUM(K6:K294)</f>
         <v/>
       </c>
-      <c r="L295" s="7">
+      <c r="L295" s="10">
         <f>SUM(L6:L294)</f>
         <v/>
       </c>
-      <c r="M295" s="7">
+      <c r="M295" s="10">
         <f>SUM(M6:M294)</f>
         <v/>
       </c>
-      <c r="N295" s="7">
+      <c r="N295" s="10">
         <f>SUM(N6:N294)</f>
         <v/>
       </c>
-      <c r="O295" s="7">
+      <c r="O295" s="10">
         <f>SUM(O6:O294)</f>
         <v/>
       </c>
-      <c r="P295" s="7">
+      <c r="P295" s="10">
         <f>SUM(P6:P294)</f>
         <v/>
       </c>
-      <c r="Q295" s="7">
+      <c r="Q295" s="10">
         <f>SUM(Q6:Q294)</f>
         <v/>
       </c>
-      <c r="R295" s="7">
+      <c r="R295" s="10">
         <f>SUM(R6:R294)</f>
         <v/>
       </c>
-      <c r="S295" s="7">
+      <c r="S295" s="10">
         <f>SUM(S6:S294)</f>
         <v/>
       </c>
-      <c r="T295" s="7">
+      <c r="T295" s="10">
         <f>SUM(T6:T294)</f>
         <v/>
       </c>
-      <c r="U295" s="7">
+      <c r="U295" s="10">
         <f>SUM(U6:U294)</f>
+        <v/>
+      </c>
+      <c r="V295" s="10">
+        <f>SUM(V6:V294)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="11" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B296" s="12" t="inlineStr"/>
+      <c r="C296" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="D296" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="13" t="n">
+        <v>257</v>
+      </c>
+      <c r="G296" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H296" s="13" t="n">
+        <v>242</v>
+      </c>
+      <c r="I296" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="J296" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" s="13" t="n">
+        <v>730</v>
+      </c>
+      <c r="S296" s="13" t="n">
+        <v>229</v>
+      </c>
+      <c r="T296" s="13" t="n">
+        <v>959</v>
+      </c>
+      <c r="U296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V296" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B297" s="15" t="inlineStr"/>
+      <c r="C297" s="16">
+        <f>C295+C296</f>
+        <v/>
+      </c>
+      <c r="D297" s="16">
+        <f>D295+D296</f>
+        <v/>
+      </c>
+      <c r="E297" s="16">
+        <f>E295+E296</f>
+        <v/>
+      </c>
+      <c r="F297" s="16">
+        <f>F295+F296</f>
+        <v/>
+      </c>
+      <c r="G297" s="16">
+        <f>G295+G296</f>
+        <v/>
+      </c>
+      <c r="H297" s="16">
+        <f>H295+H296</f>
+        <v/>
+      </c>
+      <c r="I297" s="16">
+        <f>I295+I296</f>
+        <v/>
+      </c>
+      <c r="J297" s="16">
+        <f>J295+J296</f>
+        <v/>
+      </c>
+      <c r="K297" s="16">
+        <f>K295+K296</f>
+        <v/>
+      </c>
+      <c r="L297" s="16">
+        <f>L295+L296</f>
+        <v/>
+      </c>
+      <c r="M297" s="16">
+        <f>M295+M296</f>
+        <v/>
+      </c>
+      <c r="N297" s="16">
+        <f>N295+N296</f>
+        <v/>
+      </c>
+      <c r="O297" s="16">
+        <f>O295+O296</f>
+        <v/>
+      </c>
+      <c r="P297" s="16">
+        <f>P295+P296</f>
+        <v/>
+      </c>
+      <c r="Q297" s="16">
+        <f>Q295+Q296</f>
+        <v/>
+      </c>
+      <c r="R297" s="16">
+        <f>R295+R296</f>
+        <v/>
+      </c>
+      <c r="S297" s="16">
+        <f>S295+S296</f>
+        <v/>
+      </c>
+      <c r="T297" s="16">
+        <f>T295+T296</f>
+        <v/>
+      </c>
+      <c r="U297" s="16">
+        <f>U295+U296</f>
+        <v/>
+      </c>
+      <c r="V297" s="16">
+        <f>V295+V296</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_032.xlsx
+++ b/AC_2009/AC_032.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +195,23 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -597,7 +627,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -21244,245 +21273,245 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="8" t="inlineStr">
+      <c r="A295" s="17" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B295" s="9" t="inlineStr"/>
-      <c r="C295" s="10">
+      <c r="B295" s="18" t="inlineStr"/>
+      <c r="C295" s="19">
         <f>SUM(C6:C294)</f>
         <v/>
       </c>
-      <c r="D295" s="10">
+      <c r="D295" s="19">
         <f>SUM(D6:D294)</f>
         <v/>
       </c>
-      <c r="E295" s="10">
+      <c r="E295" s="19">
         <f>SUM(E6:E294)</f>
         <v/>
       </c>
-      <c r="F295" s="10">
+      <c r="F295" s="19">
         <f>SUM(F6:F294)</f>
         <v/>
       </c>
-      <c r="G295" s="10">
+      <c r="G295" s="19">
         <f>SUM(G6:G294)</f>
         <v/>
       </c>
-      <c r="H295" s="10">
+      <c r="H295" s="19">
         <f>SUM(H6:H294)</f>
         <v/>
       </c>
-      <c r="I295" s="10">
+      <c r="I295" s="19">
         <f>SUM(I6:I294)</f>
         <v/>
       </c>
-      <c r="J295" s="10">
+      <c r="J295" s="19">
         <f>SUM(J6:J294)</f>
         <v/>
       </c>
-      <c r="K295" s="10">
+      <c r="K295" s="19">
         <f>SUM(K6:K294)</f>
         <v/>
       </c>
-      <c r="L295" s="10">
+      <c r="L295" s="19">
         <f>SUM(L6:L294)</f>
         <v/>
       </c>
-      <c r="M295" s="10">
+      <c r="M295" s="19">
         <f>SUM(M6:M294)</f>
         <v/>
       </c>
-      <c r="N295" s="10">
+      <c r="N295" s="19">
         <f>SUM(N6:N294)</f>
         <v/>
       </c>
-      <c r="O295" s="10">
+      <c r="O295" s="19">
         <f>SUM(O6:O294)</f>
         <v/>
       </c>
-      <c r="P295" s="10">
+      <c r="P295" s="19">
         <f>SUM(P6:P294)</f>
         <v/>
       </c>
-      <c r="Q295" s="10">
+      <c r="Q295" s="19">
         <f>SUM(Q6:Q294)</f>
         <v/>
       </c>
-      <c r="R295" s="10">
+      <c r="R295" s="19">
         <f>SUM(R6:R294)</f>
         <v/>
       </c>
-      <c r="S295" s="10">
+      <c r="S295" s="19">
         <f>SUM(S6:S294)</f>
         <v/>
       </c>
-      <c r="T295" s="10">
+      <c r="T295" s="19">
         <f>SUM(T6:T294)</f>
         <v/>
       </c>
-      <c r="U295" s="10">
+      <c r="U295" s="19">
         <f>SUM(U6:U294)</f>
         <v/>
       </c>
-      <c r="V295" s="10">
+      <c r="V295" s="19">
         <f>SUM(V6:V294)</f>
         <v/>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="11" t="inlineStr">
+      <c r="A296" s="20" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B296" s="12" t="inlineStr"/>
-      <c r="C296" s="13" t="n">
+      <c r="C296" s="19" t="n">
         <v>119</v>
       </c>
-      <c r="D296" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F296" s="13" t="n">
+      <c r="D296" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="19" t="n">
         <v>257</v>
       </c>
-      <c r="G296" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H296" s="13" t="n">
+      <c r="G296" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H296" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="I296" s="13" t="n">
+      <c r="I296" s="19" t="n">
         <v>103</v>
       </c>
-      <c r="J296" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R296" s="13" t="n">
+      <c r="J296" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" s="19" t="n">
         <v>730</v>
       </c>
-      <c r="S296" s="13" t="n">
+      <c r="S296" s="19" t="n">
         <v>229</v>
       </c>
-      <c r="T296" s="13" t="n">
+      <c r="T296" s="19" t="n">
         <v>959</v>
       </c>
-      <c r="U296" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V296" s="13" t="n">
+      <c r="U296" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V296" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="14" t="inlineStr">
+      <c r="A297" s="21" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B297" s="15" t="inlineStr"/>
-      <c r="C297" s="16">
+      <c r="B297" s="22" t="inlineStr"/>
+      <c r="C297" s="23">
         <f>C295+C296</f>
         <v/>
       </c>
-      <c r="D297" s="16">
+      <c r="D297" s="23">
         <f>D295+D296</f>
         <v/>
       </c>
-      <c r="E297" s="16">
+      <c r="E297" s="23">
         <f>E295+E296</f>
         <v/>
       </c>
-      <c r="F297" s="16">
+      <c r="F297" s="23">
         <f>F295+F296</f>
         <v/>
       </c>
-      <c r="G297" s="16">
+      <c r="G297" s="23">
         <f>G295+G296</f>
         <v/>
       </c>
-      <c r="H297" s="16">
+      <c r="H297" s="23">
         <f>H295+H296</f>
         <v/>
       </c>
-      <c r="I297" s="16">
+      <c r="I297" s="23">
         <f>I295+I296</f>
         <v/>
       </c>
-      <c r="J297" s="16">
+      <c r="J297" s="23">
         <f>J295+J296</f>
         <v/>
       </c>
-      <c r="K297" s="16">
+      <c r="K297" s="23">
         <f>K295+K296</f>
         <v/>
       </c>
-      <c r="L297" s="16">
+      <c r="L297" s="23">
         <f>L295+L296</f>
         <v/>
       </c>
-      <c r="M297" s="16">
+      <c r="M297" s="23">
         <f>M295+M296</f>
         <v/>
       </c>
-      <c r="N297" s="16">
+      <c r="N297" s="23">
         <f>N295+N296</f>
         <v/>
       </c>
-      <c r="O297" s="16">
+      <c r="O297" s="23">
         <f>O295+O296</f>
         <v/>
       </c>
-      <c r="P297" s="16">
+      <c r="P297" s="23">
         <f>P295+P296</f>
         <v/>
       </c>
-      <c r="Q297" s="16">
+      <c r="Q297" s="23">
         <f>Q295+Q296</f>
         <v/>
       </c>
-      <c r="R297" s="16">
+      <c r="R297" s="23">
         <f>R295+R296</f>
         <v/>
       </c>
-      <c r="S297" s="16">
+      <c r="S297" s="23">
         <f>S295+S296</f>
         <v/>
       </c>
-      <c r="T297" s="16">
+      <c r="T297" s="23">
         <f>T295+T296</f>
         <v/>
       </c>
-      <c r="U297" s="16">
+      <c r="U297" s="23">
         <f>U295+U296</f>
         <v/>
       </c>
-      <c r="V297" s="16">
+      <c r="V297" s="23">
         <f>V295+V296</f>
         <v/>
       </c>

--- a/AC_2009/AC_032.xlsx
+++ b/AC_2009/AC_032.xlsx
@@ -1462,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V297"/>
+  <dimension ref="A1:U297"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" style="1" min="1" max="3"/>
@@ -1482,8 +1482,7 @@
     <col width="17" customWidth="1" style="1" min="19" max="19"/>
     <col width="16" customWidth="1" style="1" min="20" max="20"/>
     <col width="17" customWidth="1" style="1" min="21" max="21"/>
-    <col width="16" customWidth="1" style="1" min="22" max="22"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="23" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="22" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.35" customHeight="1" s="25">
@@ -1512,7 +1511,6 @@
       <c r="S1" s="3" t="n"/>
       <c r="T1" s="3" t="n"/>
       <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
     </row>
     <row r="2" ht="13.75" customHeight="1" s="25">
       <c r="A2" s="4" t="inlineStr">
@@ -1540,7 +1538,6 @@
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
-      <c r="V2" s="3" t="n"/>
     </row>
     <row r="3" ht="13.75" customHeight="1" s="25">
       <c r="A3" s="4" t="inlineStr">
@@ -1568,7 +1565,6 @@
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n"/>
     </row>
     <row r="4" ht="13.55" customHeight="1" s="25">
       <c r="A4" s="5" t="n"/>
@@ -1592,7 +1588,6 @@
       <c r="S4" s="5" t="n"/>
       <c r="T4" s="5" t="n"/>
       <c r="U4" s="5" t="n"/>
-      <c r="V4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.55" customHeight="1" s="25">
       <c r="A5" s="6" t="inlineStr">
@@ -1695,14 +1690,9 @@
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
         </is>
       </c>
     </row>
@@ -1773,9 +1763,6 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" ht="26.55" customHeight="1" s="25">
       <c r="A7" s="9" t="n">
@@ -1844,9 +1831,6 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="26.55" customHeight="1" s="25">
       <c r="A8" s="9" t="n">
@@ -1915,9 +1899,6 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" ht="26.55" customHeight="1" s="25">
       <c r="A9" s="9" t="n">
@@ -1986,9 +1967,6 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="26.55" customHeight="1" s="25">
       <c r="A10" s="9" t="n">
@@ -2057,9 +2035,6 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" ht="26.55" customHeight="1" s="25">
       <c r="A11" s="9" t="n">
@@ -2126,9 +2101,6 @@
         <v>442</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,9 +2172,6 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="39.55" customHeight="1" s="25">
       <c r="A13" s="9" t="n">
@@ -2272,9 +2241,6 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="39.55" customHeight="1" s="25">
       <c r="A14" s="9" t="n">
@@ -2344,9 +2310,6 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" ht="39.55" customHeight="1" s="25">
       <c r="A15" s="9" t="n">
@@ -2416,9 +2379,6 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" ht="39.55" customHeight="1" s="25">
       <c r="A16" s="9" t="n">
@@ -2488,9 +2448,6 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" ht="26.55" customHeight="1" s="25">
       <c r="A17" s="9" t="n">
@@ -2559,9 +2516,6 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" ht="26.55" customHeight="1" s="25">
       <c r="A18" s="9" t="n">
@@ -2630,9 +2584,6 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" ht="26.55" customHeight="1" s="25">
       <c r="A19" s="9" t="n">
@@ -2701,9 +2652,6 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="26.55" customHeight="1" s="25">
       <c r="A20" s="9" t="n">
@@ -2772,9 +2720,6 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" ht="26.55" customHeight="1" s="25">
       <c r="A21" s="9" t="n">
@@ -2843,9 +2788,6 @@
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" ht="26.55" customHeight="1" s="25">
       <c r="A22" s="9" t="n">
@@ -2914,9 +2856,6 @@
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23" ht="13.55" customHeight="1" s="25">
       <c r="A23" s="9" t="n">
@@ -2984,9 +2923,6 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" ht="26.55" customHeight="1" s="25">
       <c r="A24" s="9" t="n">
@@ -3055,9 +2991,6 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" ht="26.55" customHeight="1" s="25">
       <c r="A25" s="9" t="n">
@@ -3126,9 +3059,6 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" ht="26.55" customHeight="1" s="25">
       <c r="A26" s="9" t="n">
@@ -3197,9 +3127,6 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="26.55" customHeight="1" s="25">
       <c r="A27" s="9" t="n">
@@ -3268,9 +3195,6 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" ht="26.55" customHeight="1" s="25">
       <c r="A28" s="9" t="n">
@@ -3339,9 +3263,6 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" ht="26.55" customHeight="1" s="25">
       <c r="A29" s="9" t="n">
@@ -3410,9 +3331,6 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" ht="39.55" customHeight="1" s="25">
       <c r="A30" s="9" t="n">
@@ -3482,9 +3400,6 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" ht="26.55" customHeight="1" s="25">
       <c r="A31" s="9" t="n">
@@ -3553,9 +3468,6 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32" ht="26.55" customHeight="1" s="25">
       <c r="A32" s="9" t="n">
@@ -3624,9 +3536,6 @@
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" ht="26.55" customHeight="1" s="25">
       <c r="A33" s="9" t="n">
@@ -3695,9 +3604,6 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="26.55" customHeight="1" s="25">
       <c r="A34" s="9" t="n">
@@ -3766,9 +3672,6 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" ht="26.55" customHeight="1" s="25">
       <c r="A35" s="9" t="n">
@@ -3837,9 +3740,6 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" ht="26.55" customHeight="1" s="25">
       <c r="A36" s="9" t="n">
@@ -3908,9 +3808,6 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" ht="26.55" customHeight="1" s="25">
       <c r="A37" s="9" t="n">
@@ -3979,9 +3876,6 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" ht="26.55" customHeight="1" s="25">
       <c r="A38" s="9" t="n">
@@ -4050,9 +3944,6 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" ht="39.55" customHeight="1" s="25">
       <c r="A39" s="9" t="n">
@@ -4122,9 +4013,6 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" ht="39.55" customHeight="1" s="25">
       <c r="A40" s="9" t="n">
@@ -4194,9 +4082,6 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" ht="26.55" customHeight="1" s="25">
       <c r="A41" s="9" t="n">
@@ -4265,9 +4150,6 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42" ht="26.55" customHeight="1" s="25">
       <c r="A42" s="9" t="n">
@@ -4336,9 +4218,6 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" ht="26.55" customHeight="1" s="25">
       <c r="A43" s="9" t="n">
@@ -4407,9 +4286,6 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" ht="26.55" customHeight="1" s="25">
       <c r="A44" s="9" t="n">
@@ -4478,9 +4354,6 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" ht="26.55" customHeight="1" s="25">
       <c r="A45" s="9" t="n">
@@ -4549,9 +4422,6 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" ht="26.55" customHeight="1" s="25">
       <c r="A46" s="9" t="n">
@@ -4620,9 +4490,6 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47" ht="26.55" customHeight="1" s="25">
       <c r="A47" s="9" t="n">
@@ -4691,9 +4558,6 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="48" ht="26.55" customHeight="1" s="25">
       <c r="A48" s="9" t="n">
@@ -4762,9 +4626,6 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49" ht="39.55" customHeight="1" s="25">
       <c r="A49" s="9" t="n">
@@ -4834,9 +4695,6 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50" ht="26.55" customHeight="1" s="25">
       <c r="A50" s="9" t="n">
@@ -4905,9 +4763,6 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51" ht="26.55" customHeight="1" s="25">
       <c r="A51" s="9" t="n">
@@ -4976,9 +4831,6 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52" ht="26.55" customHeight="1" s="25">
       <c r="A52" s="9" t="n">
@@ -5047,9 +4899,6 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="53" ht="26.55" customHeight="1" s="25">
       <c r="A53" s="9" t="n">
@@ -5118,9 +4967,6 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="54" ht="26.55" customHeight="1" s="25">
       <c r="A54" s="9" t="n">
@@ -5189,9 +5035,6 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="55" ht="26.55" customHeight="1" s="25">
       <c r="A55" s="9" t="n">
@@ -5260,9 +5103,6 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56" ht="26.55" customHeight="1" s="25">
       <c r="A56" s="9" t="n">
@@ -5331,9 +5171,6 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57" ht="26.55" customHeight="1" s="25">
       <c r="A57" s="9" t="n">
@@ -5402,9 +5239,6 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58" ht="26.55" customHeight="1" s="25">
       <c r="A58" s="9" t="n">
@@ -5473,9 +5307,6 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59" ht="26.55" customHeight="1" s="25">
       <c r="A59" s="9" t="n">
@@ -5544,9 +5375,6 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60" ht="39.55" customHeight="1" s="25">
       <c r="A60" s="9" t="n">
@@ -5616,9 +5444,6 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61" ht="26.55" customHeight="1" s="25">
       <c r="A61" s="9" t="n">
@@ -5687,9 +5512,6 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62" ht="26.55" customHeight="1" s="25">
       <c r="A62" s="9" t="n">
@@ -5758,9 +5580,6 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63" ht="26.55" customHeight="1" s="25">
       <c r="A63" s="9" t="n">
@@ -5829,9 +5648,6 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64" ht="26.55" customHeight="1" s="25">
       <c r="A64" s="9" t="n">
@@ -5900,9 +5716,6 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65" ht="26.55" customHeight="1" s="25">
       <c r="A65" s="9" t="n">
@@ -5971,9 +5784,6 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" ht="26.55" customHeight="1" s="25">
       <c r="A66" s="9" t="n">
@@ -6042,9 +5852,6 @@
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" ht="26.55" customHeight="1" s="25">
       <c r="A67" s="9" t="n">
@@ -6113,9 +5920,6 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" ht="26.55" customHeight="1" s="25">
       <c r="A68" s="9" t="n">
@@ -6184,9 +5988,6 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69" ht="26.55" customHeight="1" s="25">
       <c r="A69" s="9" t="n">
@@ -6255,9 +6056,6 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70" ht="26.55" customHeight="1" s="25">
       <c r="A70" s="9" t="n">
@@ -6326,9 +6124,6 @@
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71" ht="13.55" customHeight="1" s="25">
       <c r="A71" s="9" t="n">
@@ -6396,9 +6191,6 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72" ht="26.55" customHeight="1" s="25">
       <c r="A72" s="9" t="n">
@@ -6467,9 +6259,6 @@
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" ht="26.55" customHeight="1" s="25">
       <c r="A73" s="9" t="n">
@@ -6538,9 +6327,6 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" ht="26.55" customHeight="1" s="25">
       <c r="A74" s="9" t="n">
@@ -6609,9 +6395,6 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" ht="26.55" customHeight="1" s="25">
       <c r="A75" s="9" t="n">
@@ -6680,9 +6463,6 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" ht="26.55" customHeight="1" s="25">
       <c r="A76" s="9" t="n">
@@ -6751,9 +6531,6 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" ht="26.55" customHeight="1" s="25">
       <c r="A77" s="9" t="n">
@@ -6822,9 +6599,6 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78" ht="26.55" customHeight="1" s="25">
       <c r="A78" s="9" t="n">
@@ -6893,9 +6667,6 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" ht="13.55" customHeight="1" s="25">
       <c r="A79" s="9" t="n">
@@ -6963,9 +6734,6 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" ht="26.55" customHeight="1" s="25">
       <c r="A80" s="9" t="n">
@@ -7034,9 +6802,6 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81" ht="26.55" customHeight="1" s="25">
       <c r="A81" s="9" t="n">
@@ -7105,9 +6870,6 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82" ht="26.55" customHeight="1" s="25">
       <c r="A82" s="9" t="n">
@@ -7176,9 +6938,6 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83" ht="26.55" customHeight="1" s="25">
       <c r="A83" s="9" t="n">
@@ -7247,9 +7006,6 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84" ht="39.55" customHeight="1" s="25">
       <c r="A84" s="9" t="n">
@@ -7319,9 +7075,6 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" ht="39.55" customHeight="1" s="25">
       <c r="A85" s="9" t="n">
@@ -7391,9 +7144,6 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" ht="26.55" customHeight="1" s="25">
       <c r="A86" s="9" t="n">
@@ -7462,9 +7212,6 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87" ht="26.55" customHeight="1" s="25">
       <c r="A87" s="9" t="n">
@@ -7533,9 +7280,6 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88" ht="26.55" customHeight="1" s="25">
       <c r="A88" s="9" t="n">
@@ -7604,9 +7348,6 @@
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89" ht="26.55" customHeight="1" s="25">
       <c r="A89" s="9" t="n">
@@ -7675,9 +7416,6 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="90" ht="26.55" customHeight="1" s="25">
       <c r="A90" s="9" t="n">
@@ -7746,9 +7484,6 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" ht="26.55" customHeight="1" s="25">
       <c r="A91" s="9" t="n">
@@ -7817,9 +7552,6 @@
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92" ht="26.55" customHeight="1" s="25">
       <c r="A92" s="9" t="n">
@@ -7888,9 +7620,6 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="93" ht="26.55" customHeight="1" s="25">
       <c r="A93" s="9" t="n">
@@ -7959,9 +7688,6 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94" ht="26.55" customHeight="1" s="25">
       <c r="A94" s="9" t="n">
@@ -8030,9 +7756,6 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95" ht="26.55" customHeight="1" s="25">
       <c r="A95" s="9" t="n">
@@ -8101,9 +7824,6 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96" ht="26.55" customHeight="1" s="25">
       <c r="A96" s="9" t="n">
@@ -8172,9 +7892,6 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97" ht="26.55" customHeight="1" s="25">
       <c r="A97" s="9" t="n">
@@ -8243,9 +7960,6 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98" ht="26.55" customHeight="1" s="25">
       <c r="A98" s="9" t="n">
@@ -8314,9 +8028,6 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99" ht="26.55" customHeight="1" s="25">
       <c r="A99" s="9" t="n">
@@ -8385,9 +8096,6 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100" ht="26.55" customHeight="1" s="25">
       <c r="A100" s="9" t="n">
@@ -8456,9 +8164,6 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101" ht="26.55" customHeight="1" s="25">
       <c r="A101" s="9" t="n">
@@ -8527,9 +8232,6 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102" ht="26.55" customHeight="1" s="25">
       <c r="A102" s="9" t="n">
@@ -8598,9 +8300,6 @@
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103" ht="26.55" customHeight="1" s="25">
       <c r="A103" s="9" t="n">
@@ -8669,9 +8368,6 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" ht="26.55" customHeight="1" s="25">
       <c r="A104" s="9" t="n">
@@ -8740,9 +8436,6 @@
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105" ht="26.55" customHeight="1" s="25">
       <c r="A105" s="9" t="n">
@@ -8811,9 +8504,6 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="106" ht="26.55" customHeight="1" s="25">
       <c r="A106" s="9" t="n">
@@ -8882,9 +8572,6 @@
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" ht="26.55" customHeight="1" s="25">
       <c r="A107" s="9" t="n">
@@ -8953,9 +8640,6 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="108" ht="26.55" customHeight="1" s="25">
       <c r="A108" s="9" t="n">
@@ -9024,9 +8708,6 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109" ht="26.55" customHeight="1" s="25">
       <c r="A109" s="9" t="n">
@@ -9095,9 +8776,6 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="110" ht="26.55" customHeight="1" s="25">
       <c r="A110" s="9" t="n">
@@ -9166,9 +8844,6 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="111" ht="26.55" customHeight="1" s="25">
       <c r="A111" s="9" t="n">
@@ -9237,9 +8912,6 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" ht="26.55" customHeight="1" s="25">
       <c r="A112" s="9" t="n">
@@ -9308,9 +8980,6 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113" ht="26.55" customHeight="1" s="25">
       <c r="A113" s="9" t="n">
@@ -9379,9 +9048,6 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114" ht="26.55" customHeight="1" s="25">
       <c r="A114" s="9" t="n">
@@ -9450,9 +9116,6 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" ht="26.55" customHeight="1" s="25">
       <c r="A115" s="9" t="n">
@@ -9521,9 +9184,6 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="116" ht="26.55" customHeight="1" s="25">
       <c r="A116" s="9" t="n">
@@ -9592,9 +9252,6 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="117" ht="26.55" customHeight="1" s="25">
       <c r="A117" s="9" t="n">
@@ -9663,9 +9320,6 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="118" ht="26.55" customHeight="1" s="25">
       <c r="A118" s="9" t="n">
@@ -9734,9 +9388,6 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119" ht="26.55" customHeight="1" s="25">
       <c r="A119" s="9" t="n">
@@ -9805,9 +9456,6 @@
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120" ht="26.55" customHeight="1" s="25">
       <c r="A120" s="9" t="n">
@@ -9876,9 +9524,6 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="121" ht="26.55" customHeight="1" s="25">
       <c r="A121" s="9" t="n">
@@ -9947,9 +9592,6 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122" ht="26.55" customHeight="1" s="25">
       <c r="A122" s="9" t="n">
@@ -10018,9 +9660,6 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123" ht="26.55" customHeight="1" s="25">
       <c r="A123" s="9" t="n">
@@ -10089,9 +9728,6 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124" ht="26.55" customHeight="1" s="25">
       <c r="A124" s="9" t="n">
@@ -10160,9 +9796,6 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="125" ht="26.55" customHeight="1" s="25">
       <c r="A125" s="9" t="n">
@@ -10231,9 +9864,6 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="126" ht="26.55" customHeight="1" s="25">
       <c r="A126" s="9" t="n">
@@ -10302,9 +9932,6 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="127" ht="26.55" customHeight="1" s="25">
       <c r="A127" s="9" t="n">
@@ -10373,9 +10000,6 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128" ht="26.55" customHeight="1" s="25">
       <c r="A128" s="9" t="n">
@@ -10444,9 +10068,6 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129" ht="39.55" customHeight="1" s="25">
       <c r="A129" s="9" t="n">
@@ -10516,9 +10137,6 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="130" ht="26.55" customHeight="1" s="25">
       <c r="A130" s="9" t="n">
@@ -10587,9 +10205,6 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131" ht="26.55" customHeight="1" s="25">
       <c r="A131" s="9" t="n">
@@ -10658,9 +10273,6 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132" ht="26.55" customHeight="1" s="25">
       <c r="A132" s="9" t="n">
@@ -10729,9 +10341,6 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133" ht="26.55" customHeight="1" s="25">
       <c r="A133" s="9" t="n">
@@ -10800,9 +10409,6 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134" ht="39.55" customHeight="1" s="25">
       <c r="A134" s="9" t="n">
@@ -10872,9 +10478,6 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135" ht="26.55" customHeight="1" s="25">
       <c r="A135" s="9" t="n">
@@ -10943,9 +10546,6 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136" ht="26.55" customHeight="1" s="25">
       <c r="A136" s="9" t="n">
@@ -11014,9 +10614,6 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137" ht="26.55" customHeight="1" s="25">
       <c r="A137" s="9" t="n">
@@ -11085,9 +10682,6 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" ht="26.55" customHeight="1" s="25">
       <c r="A138" s="9" t="n">
@@ -11156,9 +10750,6 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" ht="26.55" customHeight="1" s="25">
       <c r="A139" s="9" t="n">
@@ -11227,9 +10818,6 @@
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" ht="26.55" customHeight="1" s="25">
       <c r="A140" s="9" t="n">
@@ -11298,9 +10886,6 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="141" ht="26.55" customHeight="1" s="25">
       <c r="A141" s="9" t="n">
@@ -11369,9 +10954,6 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142" ht="26.55" customHeight="1" s="25">
       <c r="A142" s="9" t="n">
@@ -11440,9 +11022,6 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143" ht="26.55" customHeight="1" s="25">
       <c r="A143" s="9" t="n">
@@ -11511,9 +11090,6 @@
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="144" ht="26.55" customHeight="1" s="25">
       <c r="A144" s="9" t="n">
@@ -11582,9 +11158,6 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="145" ht="26.55" customHeight="1" s="25">
       <c r="A145" s="9" t="n">
@@ -11653,9 +11226,6 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="146" ht="26.55" customHeight="1" s="25">
       <c r="A146" s="9" t="n">
@@ -11722,9 +11292,6 @@
         <v>717</v>
       </c>
       <c r="U146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11797,9 +11364,6 @@
       <c r="U147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148" ht="26.55" customHeight="1" s="25">
       <c r="A148" s="9" t="n">
@@ -11868,9 +11432,6 @@
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="149" ht="39.55" customHeight="1" s="25">
       <c r="A149" s="9" t="n">
@@ -11940,9 +11501,6 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="150" ht="39.55" customHeight="1" s="25">
       <c r="A150" s="9" t="n">
@@ -12012,9 +11570,6 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="151" ht="39.55" customHeight="1" s="25">
       <c r="A151" s="9" t="n">
@@ -12084,9 +11639,6 @@
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="152" ht="26.55" customHeight="1" s="25">
       <c r="A152" s="9" t="n">
@@ -12155,9 +11707,6 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="153" ht="26.55" customHeight="1" s="25">
       <c r="A153" s="9" t="n">
@@ -12226,9 +11775,6 @@
       <c r="U153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V153" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="154" ht="39.55" customHeight="1" s="25">
       <c r="A154" s="9" t="n">
@@ -12298,9 +11844,6 @@
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="155" ht="39.55" customHeight="1" s="25">
       <c r="A155" s="9" t="n">
@@ -12370,9 +11913,6 @@
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V155" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="156" ht="26.55" customHeight="1" s="25">
       <c r="A156" s="9" t="n">
@@ -12441,9 +11981,6 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="157" ht="26.55" customHeight="1" s="25">
       <c r="A157" s="9" t="n">
@@ -12512,9 +12049,6 @@
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="158" ht="26.55" customHeight="1" s="25">
       <c r="A158" s="9" t="n">
@@ -12583,9 +12117,6 @@
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="159" ht="39.55" customHeight="1" s="25">
       <c r="A159" s="9" t="n">
@@ -12655,9 +12186,6 @@
       <c r="U159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V159" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="160" ht="39.55" customHeight="1" s="25">
       <c r="A160" s="9" t="n">
@@ -12727,9 +12255,6 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="161" ht="26.55" customHeight="1" s="25">
       <c r="A161" s="9" t="n">
@@ -12798,9 +12323,6 @@
       <c r="U161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V161" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="162" ht="39.55" customHeight="1" s="25">
       <c r="A162" s="9" t="n">
@@ -12870,9 +12392,6 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="163" ht="26.55" customHeight="1" s="25">
       <c r="A163" s="9" t="n">
@@ -12941,9 +12460,6 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="164" ht="26.55" customHeight="1" s="25">
       <c r="A164" s="9" t="n">
@@ -13012,9 +12528,6 @@
       <c r="U164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V164" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="165" ht="26.55" customHeight="1" s="25">
       <c r="A165" s="9" t="n">
@@ -13083,9 +12596,6 @@
       <c r="U165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V165" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="166" ht="26.55" customHeight="1" s="25">
       <c r="A166" s="9" t="n">
@@ -13154,9 +12664,6 @@
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="167" ht="26.55" customHeight="1" s="25">
       <c r="A167" s="9" t="n">
@@ -13225,9 +12732,6 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="168" ht="26.55" customHeight="1" s="25">
       <c r="A168" s="9" t="n">
@@ -13296,9 +12800,6 @@
       <c r="U168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V168" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="169" ht="26.55" customHeight="1" s="25">
       <c r="A169" s="9" t="n">
@@ -13367,9 +12868,6 @@
       <c r="U169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V169" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="170" ht="26.55" customHeight="1" s="25">
       <c r="A170" s="9" t="n">
@@ -13438,9 +12936,6 @@
       <c r="U170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V170" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171" ht="26.55" customHeight="1" s="25">
       <c r="A171" s="9" t="n">
@@ -13509,9 +13004,6 @@
       <c r="U171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V171" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="172" ht="26.55" customHeight="1" s="25">
       <c r="A172" s="9" t="n">
@@ -13580,9 +13072,6 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173" ht="26.55" customHeight="1" s="25">
       <c r="A173" s="9" t="n">
@@ -13651,9 +13140,6 @@
       <c r="U173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V173" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="174" ht="26.55" customHeight="1" s="25">
       <c r="A174" s="9" t="n">
@@ -13722,9 +13208,6 @@
       <c r="U174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V174" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="175" ht="26.55" customHeight="1" s="25">
       <c r="A175" s="9" t="n">
@@ -13793,9 +13276,6 @@
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="176" ht="26.55" customHeight="1" s="25">
       <c r="A176" s="9" t="n">
@@ -13864,9 +13344,6 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="177" ht="26.55" customHeight="1" s="25">
       <c r="A177" s="9" t="n">
@@ -13935,9 +13412,6 @@
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="178" ht="26.55" customHeight="1" s="25">
       <c r="A178" s="9" t="n">
@@ -14006,9 +13480,6 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="179" ht="26.55" customHeight="1" s="25">
       <c r="A179" s="9" t="n">
@@ -14077,9 +13548,6 @@
       <c r="U179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V179" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="180" ht="26.55" customHeight="1" s="25">
       <c r="A180" s="9" t="n">
@@ -14148,9 +13616,6 @@
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="181" ht="26.55" customHeight="1" s="25">
       <c r="A181" s="9" t="n">
@@ -14219,9 +13684,6 @@
       <c r="U181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V181" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="182" ht="39.55" customHeight="1" s="25">
       <c r="A182" s="9" t="n">
@@ -14291,9 +13753,6 @@
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V182" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="183" ht="26.55" customHeight="1" s="25">
       <c r="A183" s="9" t="n">
@@ -14362,9 +13821,6 @@
       <c r="U183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V183" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="184" ht="26.55" customHeight="1" s="25">
       <c r="A184" s="9" t="n">
@@ -14433,9 +13889,6 @@
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V184" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="185" ht="26.55" customHeight="1" s="25">
       <c r="A185" s="9" t="n">
@@ -14504,9 +13957,6 @@
       <c r="U185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V185" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="186" ht="26.55" customHeight="1" s="25">
       <c r="A186" s="9" t="n">
@@ -14575,9 +14025,6 @@
       <c r="U186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V186" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="187" ht="26.55" customHeight="1" s="25">
       <c r="A187" s="9" t="n">
@@ -14646,9 +14093,6 @@
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="188" ht="26.55" customHeight="1" s="25">
       <c r="A188" s="9" t="n">
@@ -14717,9 +14161,6 @@
       <c r="U188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V188" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="189" ht="26.55" customHeight="1" s="25">
       <c r="A189" s="9" t="n">
@@ -14788,9 +14229,6 @@
       <c r="U189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V189" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="190" ht="26.55" customHeight="1" s="25">
       <c r="A190" s="9" t="n">
@@ -14859,9 +14297,6 @@
       <c r="U190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V190" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="191" ht="26.55" customHeight="1" s="25">
       <c r="A191" s="9" t="n">
@@ -14930,9 +14365,6 @@
       <c r="U191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V191" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="192" ht="26.55" customHeight="1" s="25">
       <c r="A192" s="9" t="n">
@@ -15001,9 +14433,6 @@
       <c r="U192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V192" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="193" ht="26.55" customHeight="1" s="25">
       <c r="A193" s="9" t="n">
@@ -15072,9 +14501,6 @@
       <c r="U193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V193" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="194" ht="26.55" customHeight="1" s="25">
       <c r="A194" s="9" t="n">
@@ -15143,9 +14569,6 @@
       <c r="U194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V194" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="195" ht="13.55" customHeight="1" s="25">
       <c r="A195" s="9" t="n">
@@ -15213,9 +14636,6 @@
       <c r="U195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V195" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="196" ht="26.55" customHeight="1" s="25">
       <c r="A196" s="9" t="n">
@@ -15284,9 +14704,6 @@
       <c r="U196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V196" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="197" ht="26.55" customHeight="1" s="25">
       <c r="A197" s="9" t="n">
@@ -15355,9 +14772,6 @@
       <c r="U197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V197" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="198" ht="13.55" customHeight="1" s="25">
       <c r="A198" s="9" t="n">
@@ -15425,9 +14839,6 @@
       <c r="U198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V198" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="199" ht="13.55" customHeight="1" s="25">
       <c r="A199" s="9" t="n">
@@ -15495,9 +14906,6 @@
       <c r="U199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V199" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="200" ht="13.55" customHeight="1" s="25">
       <c r="A200" s="9" t="n">
@@ -15565,9 +14973,6 @@
       <c r="U200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V200" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="201" ht="26.55" customHeight="1" s="25">
       <c r="A201" s="9" t="n">
@@ -15636,9 +15041,6 @@
       <c r="U201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V201" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="202" ht="26.55" customHeight="1" s="25">
       <c r="A202" s="9" t="n">
@@ -15707,9 +15109,6 @@
       <c r="U202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V202" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="203" ht="26.55" customHeight="1" s="25">
       <c r="A203" s="9" t="n">
@@ -15778,9 +15177,6 @@
       <c r="U203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V203" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="204" ht="26.55" customHeight="1" s="25">
       <c r="A204" s="9" t="n">
@@ -15849,9 +15245,6 @@
       <c r="U204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V204" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="205" ht="26.55" customHeight="1" s="25">
       <c r="A205" s="9" t="n">
@@ -15920,9 +15313,6 @@
       <c r="U205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V205" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="206" ht="26.55" customHeight="1" s="25">
       <c r="A206" s="9" t="n">
@@ -15991,9 +15381,6 @@
       <c r="U206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V206" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="207" ht="26.55" customHeight="1" s="25">
       <c r="A207" s="9" t="n">
@@ -16062,9 +15449,6 @@
       <c r="U207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V207" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="208" ht="39.55" customHeight="1" s="25">
       <c r="A208" s="9" t="n">
@@ -16134,9 +15518,6 @@
       <c r="U208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V208" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="209" ht="26.55" customHeight="1" s="25">
       <c r="A209" s="9" t="n">
@@ -16205,9 +15586,6 @@
       <c r="U209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V209" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="210" ht="26.55" customHeight="1" s="25">
       <c r="A210" s="9" t="n">
@@ -16276,9 +15654,6 @@
       <c r="U210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V210" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="211" ht="13.55" customHeight="1" s="25">
       <c r="A211" s="9" t="n">
@@ -16346,9 +15721,6 @@
       <c r="U211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V211" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="212" ht="39.55" customHeight="1" s="25">
       <c r="A212" s="9" t="n">
@@ -16418,9 +15790,6 @@
       <c r="U212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V212" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="213" ht="26.55" customHeight="1" s="25">
       <c r="A213" s="9" t="n">
@@ -16489,9 +15858,6 @@
       <c r="U213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V213" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="214" ht="26.55" customHeight="1" s="25">
       <c r="A214" s="9" t="n">
@@ -16560,9 +15926,6 @@
       <c r="U214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V214" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="215" ht="26.55" customHeight="1" s="25">
       <c r="A215" s="9" t="n">
@@ -16631,9 +15994,6 @@
       <c r="U215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V215" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="216" ht="39.55" customHeight="1" s="25">
       <c r="A216" s="9" t="n">
@@ -16703,9 +16063,6 @@
       <c r="U216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V216" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="217" ht="26.55" customHeight="1" s="25">
       <c r="A217" s="9" t="n">
@@ -16774,9 +16131,6 @@
       <c r="U217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V217" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="218" ht="39.55" customHeight="1" s="25">
       <c r="A218" s="9" t="n">
@@ -16846,9 +16200,6 @@
       <c r="U218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V218" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="219" ht="39.55" customHeight="1" s="25">
       <c r="A219" s="9" t="n">
@@ -16918,9 +16269,6 @@
       <c r="U219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V219" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="220" ht="26.55" customHeight="1" s="25">
       <c r="A220" s="9" t="n">
@@ -16989,9 +16337,6 @@
       <c r="U220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V220" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="221" ht="26.55" customHeight="1" s="25">
       <c r="A221" s="9" t="n">
@@ -17060,9 +16405,6 @@
       <c r="U221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V221" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="222" ht="39.55" customHeight="1" s="25">
       <c r="A222" s="9" t="n">
@@ -17132,9 +16474,6 @@
       <c r="U222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V222" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="223" ht="39.55" customHeight="1" s="25">
       <c r="A223" s="9" t="n">
@@ -17204,9 +16543,6 @@
       <c r="U223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V223" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="224" ht="26.55" customHeight="1" s="25">
       <c r="A224" s="9" t="n">
@@ -17275,9 +16611,6 @@
       <c r="U224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V224" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="225" ht="26.55" customHeight="1" s="25">
       <c r="A225" s="9" t="n">
@@ -17346,9 +16679,6 @@
       <c r="U225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V225" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="226" ht="26.55" customHeight="1" s="25">
       <c r="A226" s="9" t="n">
@@ -17417,9 +16747,6 @@
       <c r="U226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V226" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="227" ht="26.55" customHeight="1" s="25">
       <c r="A227" s="9" t="n">
@@ -17488,9 +16815,6 @@
       <c r="U227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V227" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="228" ht="26.55" customHeight="1" s="25">
       <c r="A228" s="9" t="n">
@@ -17559,9 +16883,6 @@
       <c r="U228" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V228" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="229" ht="26.55" customHeight="1" s="25">
       <c r="A229" s="9" t="n">
@@ -17630,9 +16951,6 @@
       <c r="U229" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V229" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="230" ht="26.55" customHeight="1" s="25">
       <c r="A230" s="9" t="n">
@@ -17701,9 +17019,6 @@
       <c r="U230" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V230" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="231" ht="39.55" customHeight="1" s="25">
       <c r="A231" s="9" t="n">
@@ -17773,9 +17088,6 @@
       <c r="U231" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V231" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="232" ht="39.55" customHeight="1" s="25">
       <c r="A232" s="9" t="n">
@@ -17845,9 +17157,6 @@
       <c r="U232" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V232" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="233" ht="26.55" customHeight="1" s="25">
       <c r="A233" s="9" t="n">
@@ -17916,9 +17225,6 @@
       <c r="U233" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V233" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="234" ht="26.55" customHeight="1" s="25">
       <c r="A234" s="9" t="n">
@@ -17987,9 +17293,6 @@
       <c r="U234" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V234" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="235" ht="39.55" customHeight="1" s="25">
       <c r="A235" s="9" t="n">
@@ -18059,9 +17362,6 @@
       <c r="U235" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V235" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="236" ht="39.55" customHeight="1" s="25">
       <c r="A236" s="9" t="n">
@@ -18131,9 +17431,6 @@
       <c r="U236" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V236" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="237" ht="39.55" customHeight="1" s="25">
       <c r="A237" s="9" t="n">
@@ -18203,9 +17500,6 @@
       <c r="U237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V237" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="238" ht="39.55" customHeight="1" s="25">
       <c r="A238" s="9" t="n">
@@ -18275,9 +17569,6 @@
       <c r="U238" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V238" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="239" ht="26.55" customHeight="1" s="25">
       <c r="A239" s="9" t="n">
@@ -18346,9 +17637,6 @@
       <c r="U239" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V239" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="240" ht="39.55" customHeight="1" s="25">
       <c r="A240" s="9" t="n">
@@ -18418,9 +17706,6 @@
       <c r="U240" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V240" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="241" ht="26.55" customHeight="1" s="25">
       <c r="A241" s="9" t="n">
@@ -18489,9 +17774,6 @@
       <c r="U241" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V241" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="242" ht="26.55" customHeight="1" s="25">
       <c r="A242" s="9" t="n">
@@ -18560,9 +17842,6 @@
       <c r="U242" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V242" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="243" ht="26.55" customHeight="1" s="25">
       <c r="A243" s="9" t="n">
@@ -18631,9 +17910,6 @@
       <c r="U243" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V243" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="244" ht="26.55" customHeight="1" s="25">
       <c r="A244" s="9" t="n">
@@ -18702,9 +17978,6 @@
       <c r="U244" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V244" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="245" ht="26.55" customHeight="1" s="25">
       <c r="A245" s="9" t="n">
@@ -18773,9 +18046,6 @@
       <c r="U245" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V245" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="246" ht="26.55" customHeight="1" s="25">
       <c r="A246" s="9" t="n">
@@ -18844,9 +18114,6 @@
       <c r="U246" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V246" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="247" ht="26.55" customHeight="1" s="25">
       <c r="A247" s="9" t="n">
@@ -18915,9 +18182,6 @@
       <c r="U247" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V247" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="248" ht="26.55" customHeight="1" s="25">
       <c r="A248" s="9" t="n">
@@ -18986,9 +18250,6 @@
       <c r="U248" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V248" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="249" ht="26.55" customHeight="1" s="25">
       <c r="A249" s="9" t="n">
@@ -19057,9 +18318,6 @@
       <c r="U249" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V249" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="250" ht="26.55" customHeight="1" s="25">
       <c r="A250" s="9" t="n">
@@ -19128,9 +18386,6 @@
       <c r="U250" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V250" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="251" ht="26.55" customHeight="1" s="25">
       <c r="A251" s="9" t="n">
@@ -19199,9 +18454,6 @@
       <c r="U251" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V251" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="252" ht="13.55" customHeight="1" s="25">
       <c r="A252" s="9" t="n">
@@ -19269,9 +18521,6 @@
       <c r="U252" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V252" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="253" ht="26.55" customHeight="1" s="25">
       <c r="A253" s="9" t="n">
@@ -19340,9 +18589,6 @@
       <c r="U253" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V253" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="254" ht="26.55" customHeight="1" s="25">
       <c r="A254" s="9" t="n">
@@ -19411,9 +18657,6 @@
       <c r="U254" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V254" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="255" ht="26.55" customHeight="1" s="25">
       <c r="A255" s="9" t="n">
@@ -19482,9 +18725,6 @@
       <c r="U255" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V255" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="256" ht="13.55" customHeight="1" s="25">
       <c r="A256" s="9" t="n">
@@ -19552,9 +18792,6 @@
       <c r="U256" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V256" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="257" ht="13.55" customHeight="1" s="25">
       <c r="A257" s="9" t="n">
@@ -19622,9 +18859,6 @@
       <c r="U257" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V257" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="258" ht="13.55" customHeight="1" s="25">
       <c r="A258" s="9" t="n">
@@ -19692,9 +18926,6 @@
       <c r="U258" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V258" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="259" ht="26.55" customHeight="1" s="25">
       <c r="A259" s="9" t="n">
@@ -19763,9 +18994,6 @@
       <c r="U259" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V259" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="260" ht="26.55" customHeight="1" s="25">
       <c r="A260" s="9" t="n">
@@ -19834,9 +19062,6 @@
       <c r="U260" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V260" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="261" ht="26.55" customHeight="1" s="25">
       <c r="A261" s="9" t="n">
@@ -19905,9 +19130,6 @@
       <c r="U261" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V261" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="262" ht="26.55" customHeight="1" s="25">
       <c r="A262" s="9" t="n">
@@ -19976,9 +19198,6 @@
       <c r="U262" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V262" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="263" ht="26.55" customHeight="1" s="25">
       <c r="A263" s="9" t="n">
@@ -20047,9 +19266,6 @@
       <c r="U263" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V263" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="264" ht="26.55" customHeight="1" s="25">
       <c r="A264" s="9" t="n">
@@ -20118,9 +19334,6 @@
       <c r="U264" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V264" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="265" ht="26.55" customHeight="1" s="25">
       <c r="A265" s="9" t="n">
@@ -20189,9 +19402,6 @@
       <c r="U265" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V265" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="266" ht="13.55" customHeight="1" s="25">
       <c r="A266" s="9" t="n">
@@ -20259,9 +19469,6 @@
       <c r="U266" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V266" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="267" ht="26.55" customHeight="1" s="25">
       <c r="A267" s="9" t="n">
@@ -20330,9 +19537,6 @@
       <c r="U267" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V267" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="268" ht="26.55" customHeight="1" s="25">
       <c r="A268" s="9" t="n">
@@ -20401,9 +19605,6 @@
       <c r="U268" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V268" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="269" ht="13.55" customHeight="1" s="25">
       <c r="A269" s="9" t="n">
@@ -20471,9 +19672,6 @@
       <c r="U269" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V269" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="270" ht="13.55" customHeight="1" s="25">
       <c r="A270" s="9" t="n">
@@ -20541,9 +19739,6 @@
       <c r="U270" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V270" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="271" ht="13.55" customHeight="1" s="25">
       <c r="A271" s="9" t="n">
@@ -20611,9 +19806,6 @@
       <c r="U271" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V271" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="272" ht="13.55" customHeight="1" s="25">
       <c r="A272" s="9" t="n">
@@ -20681,9 +19873,6 @@
       <c r="U272" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V272" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="273" ht="26.55" customHeight="1" s="25">
       <c r="A273" s="9" t="n">
@@ -20752,9 +19941,6 @@
       <c r="U273" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V273" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="274" ht="26.55" customHeight="1" s="25">
       <c r="A274" s="9" t="n">
@@ -20823,9 +20009,6 @@
       <c r="U274" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V274" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="275" ht="13.55" customHeight="1" s="25">
       <c r="A275" s="9" t="n">
@@ -20893,9 +20076,6 @@
       <c r="U275" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V275" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="276" ht="13.55" customHeight="1" s="25">
       <c r="A276" s="9" t="n">
@@ -20963,9 +20143,6 @@
       <c r="U276" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V276" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="277" ht="26.55" customHeight="1" s="25">
       <c r="A277" s="9" t="n">
@@ -21034,9 +20211,6 @@
       <c r="U277" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V277" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="278" ht="26.55" customHeight="1" s="25">
       <c r="A278" s="9" t="n">
@@ -21105,9 +20279,6 @@
       <c r="U278" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V278" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="279" ht="26.55" customHeight="1" s="25">
       <c r="A279" s="9" t="n">
@@ -21176,9 +20347,6 @@
       <c r="U279" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V279" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="280" ht="26.55" customHeight="1" s="25">
       <c r="A280" s="9" t="n">
@@ -21247,9 +20415,6 @@
       <c r="U280" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V280" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="281" ht="13.55" customHeight="1" s="25">
       <c r="A281" s="9" t="n">
@@ -21317,9 +20482,6 @@
       <c r="U281" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V281" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="282" ht="26.55" customHeight="1" s="25">
       <c r="A282" s="9" t="n">
@@ -21388,9 +20550,6 @@
       <c r="U282" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V282" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="283" ht="13.55" customHeight="1" s="25">
       <c r="A283" s="9" t="n">
@@ -21458,9 +20617,6 @@
       <c r="U283" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V283" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="284" ht="13.55" customHeight="1" s="25">
       <c r="A284" s="9" t="n">
@@ -21528,9 +20684,6 @@
       <c r="U284" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V284" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="285" ht="26.55" customHeight="1" s="25">
       <c r="A285" s="9" t="n">
@@ -21599,9 +20752,6 @@
       <c r="U285" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V285" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="286" ht="26.55" customHeight="1" s="25">
       <c r="A286" s="9" t="n">
@@ -21670,9 +20820,6 @@
       <c r="U286" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V286" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="287" ht="26.55" customHeight="1" s="25">
       <c r="A287" s="9" t="n">
@@ -21741,9 +20888,6 @@
       <c r="U287" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V287" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="288" ht="26.55" customHeight="1" s="25">
       <c r="A288" s="9" t="n">
@@ -21812,9 +20956,6 @@
       <c r="U288" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V288" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="289" ht="26.55" customHeight="1" s="25">
       <c r="A289" s="9" t="n">
@@ -21883,9 +21024,6 @@
       <c r="U289" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V289" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="290" ht="13.55" customHeight="1" s="25">
       <c r="A290" s="9" t="n">
@@ -21953,9 +21091,6 @@
       <c r="U290" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V290" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="291" ht="13.55" customHeight="1" s="25">
       <c r="A291" s="9" t="n">
@@ -22023,9 +21158,6 @@
       <c r="U291" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V291" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="292" ht="13.55" customHeight="1" s="25">
       <c r="A292" s="9" t="n">
@@ -22093,9 +21225,6 @@
       <c r="U292" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V292" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="293" ht="26.55" customHeight="1" s="25">
       <c r="A293" s="9" t="n">
@@ -22164,9 +21293,6 @@
       <c r="U293" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V293" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="294" ht="27.05" customHeight="1" s="25">
       <c r="A294" s="12" t="n">
@@ -22235,9 +21361,6 @@
       <c r="U294" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V294" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="295" ht="14.15" customHeight="1" s="25">
       <c r="A295" s="15" t="inlineStr">
@@ -22303,9 +21426,6 @@
       <c r="U295" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="V295" s="17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="296" ht="13.65" customHeight="1" s="25">
       <c r="A296" s="18" t="inlineStr">
@@ -22371,9 +21491,6 @@
       <c r="U296" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="V296" s="17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="297" ht="13.65" customHeight="1" s="25">
       <c r="A297" s="20" t="inlineStr">
@@ -22436,10 +21553,7 @@
       <c r="T297" s="23" t="n">
         <v>164895</v>
       </c>
-      <c r="U297" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V297" s="24" t="n">
+      <c r="U297" s="24" t="n">
         <v>0</v>
       </c>
     </row>
